--- a/countries/se-ac/2026-2029.xlsx
+++ b/countries/se-ac/2026-2029.xlsx
@@ -63223,10 +63223,10 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O445" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="U445" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="16">

--- a/countries/se-ac/2026-2029.xlsx
+++ b/countries/se-ac/2026-2029.xlsx
@@ -63223,10 +63223,10 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O445" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U445" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="16">
